--- a/doc/器件购买清单.xlsx
+++ b/doc/器件购买清单.xlsx
@@ -1,64 +1,533 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView windowWidth="24228" windowHeight="12540"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+  <si>
+    <t>2025年电赛支出清单</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>金额/RMB</t>
+  </si>
+  <si>
+    <t>经手人</t>
+  </si>
+  <si>
+    <t>购买日期</t>
+  </si>
+  <si>
+    <t>已均</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>DAP Link</t>
+  </si>
+  <si>
+    <t>1个</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>张雨萱</t>
+  </si>
+  <si>
+    <t>2025年4月17日</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>ADC9226</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>赵坚楷</t>
+  </si>
+  <si>
+    <t>2025年5月1日</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>FPGA开发板XILINX XC7A35T</t>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -66,18 +535,345 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,102 +1193,430 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="15.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.2" style="1" customWidth="1"/>
+    <col min="3" max="6" width="15.5" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>2025年电赛支出清单</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>序号</v>
-      </c>
-      <c r="B2" t="str">
-        <v>名称</v>
-      </c>
-      <c r="C2" t="str">
-        <v>数量</v>
-      </c>
-      <c r="D2" t="str">
-        <v>金额</v>
-      </c>
-      <c r="E2" t="str">
-        <v>经手人</v>
-      </c>
-      <c r="F2" t="str">
-        <v>购买日期</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
+    <row r="1" ht="25.8" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="str">
-        <v>DAP Link</v>
-      </c>
-      <c r="C3" t="str">
-        <v>1个</v>
-      </c>
-      <c r="D3" t="str">
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="str">
-        <v>张雨萱</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2025年4月17日</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2</v>
-      </c>
-      <c r="B4" t="str">
-        <v>ADC9226</v>
-      </c>
-      <c r="C4" t="str">
-        <v>1个</v>
-      </c>
-      <c r="D4" t="str">
-        <v>70</v>
-      </c>
-      <c r="E4" t="str">
-        <v>赵坚楷</v>
-      </c>
-      <c r="F4" t="str">
-        <v>2025年5月1日</v>
-      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5">
+        <v>228</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="6">
+        <v>45796</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError sqref="A1:F1 A2:C2 E2:F2 A3:F3 B4:F4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/doc/器件购买清单.xlsx
+++ b/doc/器件购买清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24228" windowHeight="12540"/>
+    <workbookView windowWidth="28128" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="65">
   <si>
     <t>2025年电赛支出清单</t>
   </si>
@@ -39,7 +39,7 @@
     <t>购买日期</t>
   </si>
   <si>
-    <t>已均</t>
+    <t>已A</t>
   </si>
   <si>
     <t>1</t>
@@ -51,122 +51,181 @@
     <t>1个</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>张雨萱</t>
   </si>
   <si>
     <t>2025年4月17日</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>ADC9226</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>赵坚楷</t>
   </si>
   <si>
     <t>2025年5月1日</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>FPGA开发板XILINX XC7A35T</t>
   </si>
   <si>
     <t>√</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>XC7A35T 下载器</t>
+  </si>
+  <si>
+    <t>2MM双排排母20Pin/40Pin</t>
+  </si>
+  <si>
+    <t>各1个</t>
+  </si>
+  <si>
+    <t>0603贴片电阻1% 43R欧姆 47R 51Ω 56R 62R 68R 75R 82R 1/10W</t>
+  </si>
+  <si>
+    <t>李文冠</t>
+  </si>
+  <si>
+    <t>0603贴片电阻1% 910R欧姆 1K 1.1K 1.2K 1.3K 1.5K 1.6K 1.8K</t>
+  </si>
+  <si>
+    <t>0603贴片电阻1% 9.1K欧姆 10K 11K 12K 13K 15K 16K 18K 1/10W</t>
+  </si>
+  <si>
+    <t>安立信高纯度无铅焊锡丝0.8mm含松香芯锡线家用免洗低温环保焊锡</t>
+  </si>
+  <si>
+    <t>欧姆龙继电器G6K-2F-Y 5VDC G6K-2F-Y 12VDC G6K-2F-Y24VDC</t>
+  </si>
+  <si>
+    <t>多格零件收纳盒透明塑料迷你小盒子螺丝电子元件组合分隔式分格箱</t>
+  </si>
+  <si>
+    <t>铜鸡眼铆钉空心铜铆钉气眼扣圈过孔铜件通芯卯钉M1.5/M2M3M4M5M6</t>
+  </si>
+  <si>
+    <t>圆头锤木柄铁锤家用手锤奶头锤子小榔头木工安装锤奶子锤五金工具</t>
+  </si>
+  <si>
+    <t>0402 0603 0805 1206 1210 贴片电容1u2.2u4.7u10u22u47u100uF50V</t>
+  </si>
+  <si>
+    <t>￥3.00</t>
+  </si>
+  <si>
+    <t>￥4.00</t>
+  </si>
+  <si>
+    <t>RG316镀银线射频同轴电缆 耐高温 馈线天线高频跳线RF信号延长线</t>
+  </si>
+  <si>
+    <t>SMA母头转BNC公头/母头 SMA公头转BNC公头/母头射频转接头连接器</t>
+  </si>
+  <si>
+    <t>SMA公头母头外螺纹内针内孔 RG178/58 SMA-J/KY/50-1.5压接馈线头</t>
+  </si>
+  <si>
+    <t>AD557JP 640 652 670 7524JPZ 7528KP KPZ 2S90APZ 831AP-REEL7</t>
+  </si>
+  <si>
+    <t>石英晶振直插2脚HC-49S无源晶体12MHZ 11.0592M 4M8M10M16M24M25M</t>
+  </si>
+  <si>
+    <t>原装正品 贴片 AS179-92LF SOT-363 单刀双掷(SPDT)RF开关芯片</t>
+  </si>
+  <si>
+    <t>全新原装 SI4010-C2-ATR SI4010-C2-GTR SI5351A-B-GTR MSOP10</t>
+  </si>
+  <si>
+    <t>全新原装 QN8027 QN8027-SANC QN8035-SANE QN8035 贴片MSOP10</t>
+  </si>
+  <si>
+    <t>全新原装 LM393 LM393DR 贴片SOP8 双电压比较器芯片</t>
+  </si>
+  <si>
+    <t>原装 RDA5807FP RDA5807M RDA5807MP 收音芯片 收音ic 贴片SOP16</t>
+  </si>
+  <si>
+    <t>FM收音机对讲机音响拉杆伸缩天线BNC7-114信号增益 万向拉伸天线</t>
+  </si>
+  <si>
+    <t>原装FC-135 3215 32.768K 32.768KHZ无源贴片晶振时钟晶体3.2*1.5</t>
+  </si>
+  <si>
+    <t>成都M哥同款：NanoVNA-H 矢量网络分析仪 天分 天线分析仪</t>
+  </si>
+  <si>
+    <t>【狂欢价】零件多格零件盒透明塑料乐高收纳盒五金电子元件工具盒分类整理盒</t>
+  </si>
+  <si>
+    <t>SMA 偏脚1.6 高频接头SMA-KE偏脚 SMA-KHD 间距1.6mm 外螺内孔</t>
+  </si>
+  <si>
+    <t>原装正品 GS8091-TR SOT23-5 高速运放替代兼容AD8091 SGM8091</t>
+  </si>
+  <si>
+    <t>原装 DAC7311IDCKR DAC7311 丝印：D73 SC706 12位数模转换器芯片</t>
+  </si>
+  <si>
+    <t>【优信电子】原装正品 74LVC1G08GW,125 SOT-353 单路2输入与门</t>
+  </si>
+  <si>
+    <t>MAX2611 4792 6160 6816 836 837EUS 821LUS MUS 822SUS+T SOT143</t>
+  </si>
+  <si>
+    <t>优质 直插电解电容 50V 47uF ±20% 体积6.3*12MM 普通/高频 50只</t>
+  </si>
+  <si>
+    <t>全新原装 AD834JRZ-R7 AD834J SOP-8 500MHz 增效器/分频器芯片ic</t>
+  </si>
+  <si>
+    <t>贴片固态电解电容6.3V10V16V25V35V50V100V47UF/100/220/470/1000</t>
+  </si>
+  <si>
+    <t>贴片进口CD4016BM 4017 4018 4020 4021 4022 4023 4024 4025BM96</t>
+  </si>
+  <si>
+    <t>原装正品 贴片 AD8361ARMZ AD8361 丝印J3A 射频检测器芯片 MSOP8</t>
+  </si>
+  <si>
+    <t>全新原装 NE564N NE564 直插 DIP16 线性集成电路</t>
+  </si>
+  <si>
+    <t>原装正品 CD4053BM96 SOIC16 CMOS三路2通道模拟多路复用器芯片</t>
+  </si>
+  <si>
+    <t>原装正品 直插 CD4046BE DIP-16 链接芯片 锁相环</t>
+  </si>
+  <si>
+    <t>AMS1117-1.2V/1.5/1.8/2.5/3.3/5.0/ADJ SOT89 SOT223 TO252 芯片</t>
+  </si>
+  <si>
+    <t>包邮 国巨0603贴片电阻包精度1% 170种共8500个 电阻样品本元件本</t>
+  </si>
+  <si>
+    <t>0603贴片电容包  90种0603贴片电容样品本 样品册 各50个 包邮</t>
+  </si>
+  <si>
+    <t>总数（按商品个数）</t>
+  </si>
+  <si>
+    <t>总金额</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
+    <numFmt numFmtId="7" formatCode="&quot;￥&quot;#,##0.00;&quot;￥&quot;\-#,##0.00"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -176,6 +235,13 @@
     </font>
     <font>
       <sz val="20"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -527,7 +593,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -545,6 +611,43 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -651,51 +754,48 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -705,116 +805,149 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1199,16 +1332,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.2" style="1" customWidth="1"/>
-    <col min="3" max="6" width="15.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="73.9" style="1" customWidth="1"/>
+    <col min="3" max="5" width="15.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.9" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.8" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
@@ -1251,44 +1386,44 @@
       <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5">
+        <v>70</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>10</v>
@@ -1297,298 +1432,1082 @@
         <v>228</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F5" s="6">
         <v>45796</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5">
+        <v>127</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="6">
+        <v>45798</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5">
+        <v>9.9</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="6">
+        <v>45814</v>
+      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="9">
+        <v>45847.9512384259</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="4" t="s">
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="4" t="s">
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>23.9</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="9">
+        <v>45847.9512384259</v>
+      </c>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4" t="s">
+      <c r="C12" s="4">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5">
+        <v>9</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="9">
+        <v>45846.5580092593</v>
+      </c>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="4" t="s">
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9.8</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="9">
+        <v>45846.5578587963</v>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="4" t="s">
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="9">
+        <v>45846.5578587963</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="4" t="s">
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>7.2</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="9">
+        <v>45846.5578587963</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="4" t="s">
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="E16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="9">
+        <v>45846.2279050926</v>
+      </c>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="4">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="E17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="4">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="4">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="4" t="s">
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
+      <c r="D19" s="5">
+        <v>14.52</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="9">
+        <v>45846.2279050926</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="4">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="4" t="s">
+      <c r="C20" s="4">
+        <v>4</v>
+      </c>
+      <c r="D20" s="5">
+        <v>10.4</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="9">
+        <v>45846.2279050926</v>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="4">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="4" t="s">
+      <c r="C21" s="4">
+        <v>40</v>
+      </c>
+      <c r="D21" s="5">
+        <v>31.8</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="9">
+        <v>45846.2279050926</v>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="4">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="4" t="s">
+      <c r="C22" s="4">
+        <v>4</v>
+      </c>
+      <c r="D22" s="5">
+        <v>17.96</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="9">
+        <v>45843.7344328704</v>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="4">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="4" t="s">
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1.69</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="9">
+        <v>45843.7344328704</v>
+      </c>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4">
+        <v>22</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="4" t="s">
+      <c r="C24" s="4">
+        <v>5</v>
+      </c>
+      <c r="D24" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="9">
+        <v>45843.4456018519</v>
+      </c>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="4" t="s">
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5">
+        <v>11.97</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="9">
+        <v>45843.4456018519</v>
+      </c>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="4">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="4" t="s">
+      <c r="C26" s="4">
+        <v>3</v>
+      </c>
+      <c r="D26" s="5">
+        <v>3.87</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="4">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="4" t="s">
+      <c r="C27" s="4">
+        <v>10</v>
+      </c>
+      <c r="D27" s="8">
+        <v>7.19</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="9">
+        <v>45843.4456018519</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="4">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="4" t="s">
+      <c r="C28" s="4">
+        <v>4</v>
+      </c>
+      <c r="D28" s="11"/>
+      <c r="E28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="4">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="4" t="s">
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5">
+        <v>6.61</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="9">
+        <v>45843.4456018519</v>
+      </c>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="4">
+        <v>28</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="4" t="s">
+      <c r="C30" s="4">
+        <v>10</v>
+      </c>
+      <c r="D30" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="9">
+        <v>45842.0503125</v>
+      </c>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="4">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="C31" s="4">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5">
+        <v>209</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="9">
+        <v>45838.1124537037</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="4">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="4">
+        <v>2</v>
+      </c>
+      <c r="D32" s="5">
+        <v>11.64</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="9">
+        <v>45826.4635648148</v>
+      </c>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4">
+        <v>31</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="4">
+        <v>40</v>
+      </c>
+      <c r="D33" s="5">
+        <v>17</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="9">
+        <v>45825.4586111111</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="4">
+        <v>32</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="4">
+        <v>15</v>
+      </c>
+      <c r="D34" s="5">
+        <v>9.62</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="9">
+        <v>45823.9277662037</v>
+      </c>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="4">
+        <v>33</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="4">
+        <v>5</v>
+      </c>
+      <c r="D35" s="5">
+        <v>12.5</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="9">
+        <v>45823.9277662037</v>
+      </c>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="4">
+        <v>34</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="4">
+        <v>10</v>
+      </c>
+      <c r="D36" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="9">
+        <v>45823.9277662037</v>
+      </c>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="4">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="4">
+        <v>4</v>
+      </c>
+      <c r="D37" s="5">
+        <v>15.96</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="9">
+        <v>45821.7290162037</v>
+      </c>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="4">
+        <v>36</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="9">
+        <v>45821.4235763889</v>
+      </c>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="4">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1</v>
+      </c>
+      <c r="D39" s="11"/>
+      <c r="E39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="9"/>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4">
+        <v>38</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="4">
+        <v>2</v>
+      </c>
+      <c r="D40" s="5">
+        <v>32.3</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="9">
+        <v>45821.4235763889</v>
+      </c>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="4">
+        <v>3</v>
+      </c>
+      <c r="D41" s="5">
+        <v>18</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="9">
+        <v>45821.4235763889</v>
+      </c>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4">
+        <v>40</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="4">
+        <v>1</v>
+      </c>
+      <c r="D42" s="5">
+        <v>15</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="9">
+        <v>45820.8386689815</v>
+      </c>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4">
+        <v>41</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="4">
+        <v>3</v>
+      </c>
+      <c r="D43" s="5">
+        <v>27.38</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="9">
+        <v>45817.9716898148</v>
+      </c>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="4">
+        <v>42</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="4">
+        <v>3</v>
+      </c>
+      <c r="D44" s="5">
+        <v>11.5</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="9">
+        <v>45817.9716898148</v>
+      </c>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4">
+        <v>43</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="4">
+        <v>5</v>
+      </c>
+      <c r="D45" s="12">
+        <v>17.4</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="9">
+        <v>45817.9716782407</v>
+      </c>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="4">
+        <v>44</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="4">
+        <v>4</v>
+      </c>
+      <c r="D46" s="12"/>
+      <c r="E46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="4">
+        <v>45</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" s="4">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F47" s="9">
+        <v>45817.9716782407</v>
+      </c>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="4">
+        <v>46</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="4">
+        <v>1</v>
+      </c>
+      <c r="D48" s="12">
+        <v>78.2</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="9">
+        <v>45817.9716782407</v>
+      </c>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="4">
+        <v>47</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="4">
+        <v>1</v>
+      </c>
+      <c r="D49" s="12"/>
+      <c r="E49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="4">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="4">
+        <v>49</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="16"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="4">
+        <v>50</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="16"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="4">
+        <v>51</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="16"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="4">
+        <v>52</v>
+      </c>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="16"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="4">
+        <v>53</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="16"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="4">
+        <v>54</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="16"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="4">
+        <v>55</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="16"/>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="4">
+        <v>56</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="16"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="4">
+        <v>57</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="16"/>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="4">
+        <v>58</v>
+      </c>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="16"/>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="16"/>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="13">
+        <f>COUNTA(B3:B50)</f>
+        <v>47</v>
+      </c>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13">
+        <f>SUM(D3:D60)</f>
+        <v>1112.86</v>
+      </c>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="15">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="F48:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 A2:C2 E2:F2 A3:F3 B4:F4" numberStoredAsText="1"/>
+    <ignoredError sqref="C4 E4:F4 A3:C3 E3:F3 E2:F2 A2:C2 A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
